--- a/backend/data/financials_by_company/1855.HK.xlsx
+++ b/backend/data/financials_by_company/1855.HK.xlsx
@@ -682,608 +682,608 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-20035750</v>
+        <v>-6293534.453872</v>
       </c>
       <c r="C2" t="n">
-        <v>0.25</v>
+        <v>0.097173</v>
       </c>
       <c r="D2" t="n">
-        <v>200891000</v>
+        <v>144874000</v>
       </c>
       <c r="E2" t="n">
-        <v>-80143000</v>
+        <v>-64766000</v>
       </c>
       <c r="F2" t="n">
-        <v>-80143000</v>
+        <v>-64766000</v>
       </c>
       <c r="G2" t="n">
-        <v>39972000</v>
+        <v>33558000</v>
       </c>
       <c r="H2" t="n">
-        <v>15245000</v>
+        <v>5632000</v>
       </c>
       <c r="I2" t="n">
-        <v>1429058000</v>
+        <v>725365000</v>
       </c>
       <c r="J2" t="n">
-        <v>120748000</v>
+        <v>80108000</v>
       </c>
       <c r="K2" t="n">
-        <v>105503000</v>
+        <v>74476000</v>
       </c>
       <c r="L2" t="n">
-        <v>-53332000</v>
+        <v>-32332000</v>
       </c>
       <c r="M2" t="n">
-        <v>60129000</v>
+        <v>37470000</v>
       </c>
       <c r="N2" t="n">
-        <v>6797000</v>
+        <v>5138000</v>
       </c>
       <c r="O2" t="n">
-        <v>100079250</v>
+        <v>92030465.546128</v>
       </c>
       <c r="P2" t="n">
-        <v>39972000</v>
+        <v>33558000</v>
       </c>
       <c r="Q2" t="n">
-        <v>1543204000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>814732000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2780000</v>
+      </c>
       <c r="S2" t="n">
-        <v>133134000</v>
+        <v>67224000</v>
       </c>
       <c r="T2" t="n">
-        <v>825000000</v>
+        <v>822288000</v>
       </c>
       <c r="U2" t="n">
-        <v>825000000</v>
+        <v>822288000</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="W2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="X2" t="n">
-        <v>39972000</v>
+        <v>33558000</v>
       </c>
       <c r="Y2" t="n">
-        <v>39972000</v>
+        <v>33558000</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>39972000</v>
+        <v>33558000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-6116000</v>
+        <v>148000</v>
       </c>
       <c r="AC2" t="n">
-        <v>46088000</v>
+        <v>33410000</v>
       </c>
       <c r="AD2" t="n">
-        <v>46088000</v>
+        <v>33410000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-714000</v>
+        <v>3596000</v>
       </c>
       <c r="AF2" t="n">
-        <v>45374000</v>
+        <v>37006000</v>
       </c>
       <c r="AG2" t="n">
-        <v>7054000</v>
+        <v>3450000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-80143000</v>
+        <v>-63596000</v>
       </c>
       <c r="AI2" t="n">
-        <v>296000</v>
+        <v>-638000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>79847000</v>
+        <v>64234000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-53332000</v>
+        <v>-32332000</v>
       </c>
       <c r="AL2" t="n">
-        <v>60129000</v>
+        <v>37470000</v>
       </c>
       <c r="AM2" t="n">
-        <v>6797000</v>
+        <v>5138000</v>
       </c>
       <c r="AN2" t="n">
-        <v>199888000</v>
+        <v>121863000</v>
       </c>
       <c r="AO2" t="n">
-        <v>114146000</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
+        <v>89367000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>4664000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>2161000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2161000</v>
+      </c>
       <c r="AS2" t="n">
-        <v>116691000</v>
+        <v>103174000</v>
       </c>
       <c r="AT2" t="n">
-        <v>34414000</v>
+        <v>28099000</v>
       </c>
       <c r="AU2" t="n">
-        <v>82277000</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
+        <v>75075000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>2780000</v>
+      </c>
       <c r="AW2" t="n">
-        <v>314034000</v>
+        <v>211230000</v>
       </c>
       <c r="AX2" t="n">
-        <v>1429058000</v>
+        <v>725365000</v>
       </c>
       <c r="AY2" t="n">
-        <v>1743092000</v>
+        <v>936595000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1743092000</v>
+        <v>936595000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-12381826.332739</v>
+        <v>-21832201.143365</v>
       </c>
       <c r="C3" t="n">
-        <v>0.112521</v>
+        <v>0.157396</v>
       </c>
       <c r="D3" t="n">
-        <v>360933000</v>
+        <v>102920000</v>
       </c>
       <c r="E3" t="n">
-        <v>-110040000</v>
+        <v>-138709000</v>
       </c>
       <c r="F3" t="n">
-        <v>-110040000</v>
+        <v>-138709000</v>
       </c>
       <c r="G3" t="n">
-        <v>135206000</v>
+        <v>-96343000</v>
       </c>
       <c r="H3" t="n">
-        <v>13107000</v>
+        <v>12957000</v>
       </c>
       <c r="I3" t="n">
-        <v>1904649000</v>
+        <v>922690000</v>
       </c>
       <c r="J3" t="n">
-        <v>250893000</v>
+        <v>-35789000</v>
       </c>
       <c r="K3" t="n">
-        <v>237786000</v>
+        <v>-48746000</v>
       </c>
       <c r="L3" t="n">
-        <v>-58686000</v>
+        <v>-60286000</v>
       </c>
       <c r="M3" t="n">
-        <v>65134000</v>
+        <v>66003000</v>
       </c>
       <c r="N3" t="n">
-        <v>6448000</v>
+        <v>5717000</v>
       </c>
       <c r="O3" t="n">
-        <v>232864173.667261</v>
+        <v>20533798.856635</v>
       </c>
       <c r="P3" t="n">
-        <v>135206000</v>
+        <v>-96343000</v>
       </c>
       <c r="Q3" t="n">
-        <v>2013073000</v>
+        <v>1025587000</v>
       </c>
       <c r="R3" t="n">
-        <v>9964000</v>
+        <v>8388000</v>
       </c>
       <c r="S3" t="n">
-        <v>240807000</v>
+        <v>-41803000</v>
       </c>
       <c r="T3" t="n">
-        <v>825000000</v>
+        <v>2475000000</v>
       </c>
       <c r="U3" t="n">
-        <v>825000000</v>
+        <v>2475000000</v>
       </c>
       <c r="V3" t="n">
-        <v>0.163333</v>
+        <v>-0.116667</v>
       </c>
       <c r="W3" t="n">
-        <v>0.163333</v>
+        <v>-0.116667</v>
       </c>
       <c r="X3" t="n">
-        <v>135206000</v>
+        <v>-96343000</v>
       </c>
       <c r="Y3" t="n">
-        <v>135206000</v>
+        <v>-96343000</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>135206000</v>
+        <v>-96343000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-18019000</v>
+        <v>345000</v>
       </c>
       <c r="AC3" t="n">
-        <v>153225000</v>
+        <v>-96688000</v>
       </c>
       <c r="AD3" t="n">
-        <v>153225000</v>
+        <v>-96688000</v>
       </c>
       <c r="AE3" t="n">
-        <v>19427000</v>
+        <v>-18061000</v>
       </c>
       <c r="AF3" t="n">
-        <v>172652000</v>
+        <v>-114749000</v>
       </c>
       <c r="AG3" t="n">
-        <v>2252000</v>
+        <v>3833000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-110040000</v>
+        <v>-138709000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-86000</v>
+        <v>231000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110126000</v>
+        <v>138478000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-58686000</v>
+        <v>-60286000</v>
       </c>
       <c r="AL3" t="n">
-        <v>65134000</v>
+        <v>66003000</v>
       </c>
       <c r="AM3" t="n">
-        <v>6448000</v>
+        <v>5717000</v>
       </c>
       <c r="AN3" t="n">
-        <v>342424000</v>
+        <v>90855000</v>
       </c>
       <c r="AO3" t="n">
-        <v>108424000</v>
+        <v>102897000</v>
       </c>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>110467000</v>
+        <v>105645000</v>
       </c>
       <c r="AT3" t="n">
-        <v>18800000</v>
+        <v>18835000</v>
       </c>
       <c r="AU3" t="n">
-        <v>91667000</v>
+        <v>86810000</v>
       </c>
       <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="n">
-        <v>450848000</v>
+        <v>193752000</v>
       </c>
       <c r="AX3" t="n">
-        <v>1904649000</v>
+        <v>922690000</v>
       </c>
       <c r="AY3" t="n">
-        <v>2355497000</v>
+        <v>1116442000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2355497000</v>
+        <v>1116442000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-21832201.143365</v>
+        <v>-12381826.332739</v>
       </c>
       <c r="C4" t="n">
-        <v>0.157396</v>
+        <v>0.112521</v>
       </c>
       <c r="D4" t="n">
-        <v>102920000</v>
+        <v>360933000</v>
       </c>
       <c r="E4" t="n">
-        <v>-138709000</v>
+        <v>-110040000</v>
       </c>
       <c r="F4" t="n">
-        <v>-138709000</v>
+        <v>-110040000</v>
       </c>
       <c r="G4" t="n">
-        <v>-96343000</v>
+        <v>135206000</v>
       </c>
       <c r="H4" t="n">
-        <v>12957000</v>
+        <v>13107000</v>
       </c>
       <c r="I4" t="n">
-        <v>922690000</v>
+        <v>1904649000</v>
       </c>
       <c r="J4" t="n">
-        <v>-35789000</v>
+        <v>250893000</v>
       </c>
       <c r="K4" t="n">
-        <v>-48746000</v>
+        <v>237786000</v>
       </c>
       <c r="L4" t="n">
-        <v>-60286000</v>
+        <v>-58686000</v>
       </c>
       <c r="M4" t="n">
-        <v>66003000</v>
+        <v>65134000</v>
       </c>
       <c r="N4" t="n">
-        <v>5717000</v>
+        <v>6448000</v>
       </c>
       <c r="O4" t="n">
-        <v>20533798.856635</v>
+        <v>232864173.667261</v>
       </c>
       <c r="P4" t="n">
-        <v>-96343000</v>
+        <v>135206000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1025587000</v>
+        <v>2013073000</v>
       </c>
       <c r="R4" t="n">
-        <v>8388000</v>
+        <v>9964000</v>
       </c>
       <c r="S4" t="n">
-        <v>-41803000</v>
+        <v>240807000</v>
       </c>
       <c r="T4" t="n">
-        <v>2475000000</v>
+        <v>825000000</v>
       </c>
       <c r="U4" t="n">
-        <v>2475000000</v>
+        <v>825000000</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.116667</v>
+        <v>0.163333</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.116667</v>
+        <v>0.163333</v>
       </c>
       <c r="X4" t="n">
-        <v>-96343000</v>
+        <v>135206000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-96343000</v>
+        <v>135206000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-96343000</v>
+        <v>135206000</v>
       </c>
       <c r="AB4" t="n">
-        <v>345000</v>
+        <v>-18019000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-96688000</v>
+        <v>153225000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-96688000</v>
+        <v>153225000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-18061000</v>
+        <v>19427000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-114749000</v>
+        <v>172652000</v>
       </c>
       <c r="AG4" t="n">
-        <v>3833000</v>
+        <v>2252000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-138709000</v>
+        <v>-110040000</v>
       </c>
       <c r="AI4" t="n">
-        <v>231000</v>
+        <v>-86000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>138478000</v>
+        <v>110126000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-60286000</v>
+        <v>-58686000</v>
       </c>
       <c r="AL4" t="n">
-        <v>66003000</v>
+        <v>65134000</v>
       </c>
       <c r="AM4" t="n">
-        <v>5717000</v>
+        <v>6448000</v>
       </c>
       <c r="AN4" t="n">
-        <v>90855000</v>
+        <v>342424000</v>
       </c>
       <c r="AO4" t="n">
-        <v>102897000</v>
+        <v>108424000</v>
       </c>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>105645000</v>
+        <v>110467000</v>
       </c>
       <c r="AT4" t="n">
-        <v>18835000</v>
+        <v>18800000</v>
       </c>
       <c r="AU4" t="n">
-        <v>86810000</v>
+        <v>91667000</v>
       </c>
       <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
-        <v>193752000</v>
+        <v>450848000</v>
       </c>
       <c r="AX4" t="n">
-        <v>922690000</v>
+        <v>1904649000</v>
       </c>
       <c r="AY4" t="n">
-        <v>1116442000</v>
+        <v>2355497000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1116442000</v>
+        <v>2355497000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-6293534.453872</v>
+        <v>-20035750</v>
       </c>
       <c r="C5" t="n">
-        <v>0.097173</v>
+        <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>144874000</v>
+        <v>200891000</v>
       </c>
       <c r="E5" t="n">
-        <v>-64766000</v>
+        <v>-80143000</v>
       </c>
       <c r="F5" t="n">
-        <v>-64766000</v>
+        <v>-80143000</v>
       </c>
       <c r="G5" t="n">
-        <v>33558000</v>
+        <v>39972000</v>
       </c>
       <c r="H5" t="n">
-        <v>5632000</v>
+        <v>15245000</v>
       </c>
       <c r="I5" t="n">
-        <v>725365000</v>
+        <v>1429058000</v>
       </c>
       <c r="J5" t="n">
-        <v>80108000</v>
+        <v>120748000</v>
       </c>
       <c r="K5" t="n">
-        <v>74476000</v>
+        <v>105503000</v>
       </c>
       <c r="L5" t="n">
-        <v>-32332000</v>
+        <v>-53332000</v>
       </c>
       <c r="M5" t="n">
-        <v>37470000</v>
+        <v>60129000</v>
       </c>
       <c r="N5" t="n">
-        <v>5138000</v>
+        <v>6797000</v>
       </c>
       <c r="O5" t="n">
-        <v>92030465.546128</v>
+        <v>100079250</v>
       </c>
       <c r="P5" t="n">
-        <v>33558000</v>
+        <v>39972000</v>
       </c>
       <c r="Q5" t="n">
-        <v>814732000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2780000</v>
-      </c>
+        <v>1543204000</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>67224000</v>
+        <v>133134000</v>
       </c>
       <c r="T5" t="n">
-        <v>822288000</v>
+        <v>825000000</v>
       </c>
       <c r="U5" t="n">
-        <v>822288000</v>
+        <v>825000000</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="X5" t="n">
-        <v>33558000</v>
+        <v>39972000</v>
       </c>
       <c r="Y5" t="n">
-        <v>33558000</v>
+        <v>39972000</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>33558000</v>
+        <v>39972000</v>
       </c>
       <c r="AB5" t="n">
-        <v>148000</v>
+        <v>-6116000</v>
       </c>
       <c r="AC5" t="n">
-        <v>33410000</v>
+        <v>46088000</v>
       </c>
       <c r="AD5" t="n">
-        <v>33410000</v>
+        <v>46088000</v>
       </c>
       <c r="AE5" t="n">
-        <v>3596000</v>
+        <v>-714000</v>
       </c>
       <c r="AF5" t="n">
-        <v>37006000</v>
+        <v>45374000</v>
       </c>
       <c r="AG5" t="n">
-        <v>3450000</v>
+        <v>7054000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-63596000</v>
+        <v>-80143000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-638000</v>
+        <v>296000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>64234000</v>
+        <v>79847000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-32332000</v>
+        <v>-53332000</v>
       </c>
       <c r="AL5" t="n">
-        <v>37470000</v>
+        <v>60129000</v>
       </c>
       <c r="AM5" t="n">
-        <v>5138000</v>
+        <v>6797000</v>
       </c>
       <c r="AN5" t="n">
-        <v>121863000</v>
+        <v>199888000</v>
       </c>
       <c r="AO5" t="n">
-        <v>89367000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>4664000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>2161000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>2161000</v>
-      </c>
+        <v>114146000</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>103174000</v>
+        <v>116691000</v>
       </c>
       <c r="AT5" t="n">
-        <v>28099000</v>
+        <v>34414000</v>
       </c>
       <c r="AU5" t="n">
-        <v>75075000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2780000</v>
-      </c>
+        <v>82277000</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
-        <v>211230000</v>
+        <v>314034000</v>
       </c>
       <c r="AX5" t="n">
-        <v>725365000</v>
+        <v>1429058000</v>
       </c>
       <c r="AY5" t="n">
-        <v>936595000</v>
+        <v>1743092000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>936595000</v>
+        <v>1743092000</v>
       </c>
     </row>
   </sheetData>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>825000000</v>
@@ -1638,46 +1638,46 @@
         <v>825000000</v>
       </c>
       <c r="D2" t="n">
-        <v>761882000</v>
+        <v>453036000</v>
       </c>
       <c r="E2" t="n">
-        <v>891747000</v>
+        <v>509988000</v>
       </c>
       <c r="F2" t="n">
-        <v>650789000</v>
+        <v>591696000</v>
       </c>
       <c r="G2" t="n">
-        <v>1553635000</v>
+        <v>1099192000</v>
       </c>
       <c r="H2" t="n">
-        <v>321359000</v>
+        <v>255724000</v>
       </c>
       <c r="I2" t="n">
-        <v>650789000</v>
+        <v>591696000</v>
       </c>
       <c r="J2" t="n">
-        <v>7086000</v>
+        <v>5423000</v>
       </c>
       <c r="K2" t="n">
-        <v>668974000</v>
+        <v>594627000</v>
       </c>
       <c r="L2" t="n">
-        <v>670822000</v>
+        <v>619627000</v>
       </c>
       <c r="M2" t="n">
-        <v>795192000</v>
+        <v>604077000</v>
       </c>
       <c r="N2" t="n">
-        <v>126218000</v>
+        <v>9450000</v>
       </c>
       <c r="O2" t="n">
-        <v>668974000</v>
+        <v>594627000</v>
       </c>
       <c r="P2" t="n">
-        <v>214719000</v>
+        <v>132668000</v>
       </c>
       <c r="Q2" t="n">
-        <v>70316000</v>
+        <v>90063000</v>
       </c>
       <c r="R2" t="n">
         <v>230000</v>
@@ -1686,146 +1686,144 @@
         <v>230000</v>
       </c>
       <c r="T2" t="n">
-        <v>3588337000</v>
+        <v>1775710000</v>
       </c>
       <c r="U2" t="n">
-        <v>9841000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1723000</v>
-      </c>
+        <v>37512000</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>1930000</v>
+        <v>10336000</v>
       </c>
       <c r="X2" t="n">
-        <v>6188000</v>
+        <v>27176000</v>
       </c>
       <c r="Y2" t="n">
-        <v>4340000</v>
+        <v>2176000</v>
       </c>
       <c r="Z2" t="n">
-        <v>1848000</v>
+        <v>25000000</v>
       </c>
       <c r="AA2" t="n">
-        <v>3578496000</v>
+        <v>1738198000</v>
       </c>
       <c r="AB2" t="n">
-        <v>885559000</v>
+        <v>482812000</v>
       </c>
       <c r="AC2" t="n">
-        <v>2746000</v>
+        <v>3247000</v>
       </c>
       <c r="AD2" t="n">
-        <v>882813000</v>
+        <v>479565000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1966242000</v>
+        <v>1099557000</v>
       </c>
       <c r="AF2" t="n">
-        <v>261228000</v>
+        <v>119845000</v>
       </c>
       <c r="AG2" t="n">
-        <v>15978000</v>
+        <v>307000</v>
       </c>
       <c r="AH2" t="n">
-        <v>110891000</v>
+        <v>35959000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1578145000</v>
+        <v>943446000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4383529000</v>
+        <v>2379787000</v>
       </c>
       <c r="AK2" t="n">
-        <v>483674000</v>
+        <v>385865000</v>
       </c>
       <c r="AL2" t="n">
-        <v>105214000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>68351000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>68351000</v>
-      </c>
+        <v>43872000</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>242520000</v>
+        <v>288464000</v>
       </c>
       <c r="AP2" t="n">
-        <v>166382000</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
+        <v>194797000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>16949000</v>
+      </c>
       <c r="AR2" t="n">
-        <v>76138000</v>
+        <v>76718000</v>
       </c>
       <c r="AS2" t="n">
-        <v>18185000</v>
+        <v>2931000</v>
       </c>
       <c r="AT2" t="n">
-        <v>18185000</v>
+        <v>2931000</v>
       </c>
       <c r="AU2" t="n">
-        <v>48859000</v>
+        <v>15971000</v>
       </c>
       <c r="AV2" t="n">
-        <v>-62106000</v>
+        <v>-18588000</v>
       </c>
       <c r="AW2" t="n">
-        <v>110965000</v>
+        <v>34559000</v>
       </c>
       <c r="AX2" t="n">
-        <v>52806000</v>
+        <v>23474000</v>
       </c>
       <c r="AY2" t="n">
-        <v>35106000</v>
+        <v>970000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>23053000</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
+        <v>10115000</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
       <c r="BB2" t="n">
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>3899855000</v>
+        <v>1993922000</v>
       </c>
       <c r="BD2" t="n">
-        <v>26449000</v>
+        <v>5370000</v>
       </c>
       <c r="BE2" t="n">
-        <v>15600000</v>
+        <v>12110000</v>
       </c>
       <c r="BF2" t="n">
-        <v>142000000</v>
+        <v>30271000</v>
       </c>
       <c r="BG2" t="n">
-        <v>14809000</v>
+        <v>25585000</v>
       </c>
       <c r="BH2" t="n">
-        <v>14809000</v>
+        <v>25585000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1262302000</v>
+        <v>867578000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>14783000</v>
+        <v>14417000</v>
       </c>
       <c r="BK2" t="n">
-        <v>2301133000</v>
+        <v>987062000</v>
       </c>
       <c r="BL2" t="n">
-        <v>122779000</v>
+        <v>51529000</v>
       </c>
       <c r="BM2" t="n">
-        <v>122779000</v>
+        <v>51529000</v>
       </c>
       <c r="BN2" t="n">
-        <v>122779000</v>
+        <v>46673000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>825000000</v>
@@ -1834,43 +1832,43 @@
         <v>825000000</v>
       </c>
       <c r="D3" t="n">
-        <v>595805000</v>
+        <v>833480000</v>
       </c>
       <c r="E3" t="n">
-        <v>809477000</v>
+        <v>1057138000</v>
       </c>
       <c r="F3" t="n">
-        <v>646445000</v>
+        <v>864034000</v>
       </c>
       <c r="G3" t="n">
-        <v>1455805000</v>
+        <v>1921466000</v>
       </c>
       <c r="H3" t="n">
-        <v>377208000</v>
+        <v>516731000</v>
       </c>
       <c r="I3" t="n">
-        <v>646445000</v>
+        <v>864034000</v>
       </c>
       <c r="J3" t="n">
-        <v>3267000</v>
+        <v>3425000</v>
       </c>
       <c r="K3" t="n">
-        <v>649595000</v>
+        <v>867753000</v>
       </c>
       <c r="L3" t="n">
-        <v>729542000</v>
+        <v>946685000</v>
       </c>
       <c r="M3" t="n">
-        <v>769469000</v>
+        <v>918015000</v>
       </c>
       <c r="N3" t="n">
-        <v>119874000</v>
+        <v>50262000</v>
       </c>
       <c r="O3" t="n">
-        <v>649595000</v>
+        <v>867753000</v>
       </c>
       <c r="P3" t="n">
-        <v>183072000</v>
+        <v>79235000</v>
       </c>
       <c r="Q3" t="n">
         <v>90063000</v>
@@ -1882,144 +1880,146 @@
         <v>230000</v>
       </c>
       <c r="T3" t="n">
-        <v>3076957000</v>
+        <v>3264969000</v>
       </c>
       <c r="U3" t="n">
-        <v>91672000</v>
+        <v>92509000</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>10476000</v>
+        <v>12762000</v>
       </c>
       <c r="X3" t="n">
-        <v>81196000</v>
+        <v>79747000</v>
       </c>
       <c r="Y3" t="n">
-        <v>1249000</v>
+        <v>815000</v>
       </c>
       <c r="Z3" t="n">
-        <v>79947000</v>
+        <v>78932000</v>
       </c>
       <c r="AA3" t="n">
-        <v>2985285000</v>
+        <v>3172460000</v>
       </c>
       <c r="AB3" t="n">
-        <v>728281000</v>
+        <v>977391000</v>
       </c>
       <c r="AC3" t="n">
-        <v>2018000</v>
+        <v>2610000</v>
       </c>
       <c r="AD3" t="n">
-        <v>726263000</v>
+        <v>974781000</v>
       </c>
       <c r="AE3" t="n">
-        <v>1654933000</v>
+        <v>1612033000</v>
       </c>
       <c r="AF3" t="n">
-        <v>159896000</v>
+        <v>261156000</v>
       </c>
       <c r="AG3" t="n">
         <v>307000</v>
       </c>
       <c r="AH3" t="n">
-        <v>105549000</v>
+        <v>113092000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1389181000</v>
+        <v>1237478000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3846426000</v>
+        <v>4182984000</v>
       </c>
       <c r="AK3" t="n">
-        <v>483933000</v>
+        <v>493793000</v>
       </c>
       <c r="AL3" t="n">
-        <v>93921000</v>
+        <v>77422000</v>
       </c>
       <c r="AM3" t="n">
-        <v>70141000</v>
+        <v>75622000</v>
       </c>
       <c r="AN3" t="n">
-        <v>70141000</v>
+        <v>75622000</v>
       </c>
       <c r="AO3" t="n">
-        <v>270151000</v>
+        <v>273172000</v>
       </c>
       <c r="AP3" t="n">
-        <v>191273000</v>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
+        <v>195660000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>75622000</v>
+      </c>
       <c r="AR3" t="n">
-        <v>78878000</v>
+        <v>77512000</v>
       </c>
       <c r="AS3" t="n">
-        <v>3150000</v>
+        <v>3719000</v>
       </c>
       <c r="AT3" t="n">
-        <v>3150000</v>
+        <v>3719000</v>
       </c>
       <c r="AU3" t="n">
-        <v>45968000</v>
+        <v>44870000</v>
       </c>
       <c r="AV3" t="n">
-        <v>-50680000</v>
+        <v>-44221000</v>
       </c>
       <c r="AW3" t="n">
-        <v>96648000</v>
+        <v>89091000</v>
       </c>
       <c r="AX3" t="n">
-        <v>49101000</v>
+        <v>46239000</v>
       </c>
       <c r="AY3" t="n">
-        <v>32904000</v>
+        <v>29243000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14643000</v>
+        <v>13609000</v>
       </c>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
         <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>3362493000</v>
+        <v>3689191000</v>
       </c>
       <c r="BD3" t="n">
-        <v>27155000</v>
+        <v>11135000</v>
       </c>
       <c r="BE3" t="n">
-        <v>20346000</v>
+        <v>22223000</v>
       </c>
       <c r="BF3" t="n">
-        <v>88493000</v>
+        <v>22755000</v>
       </c>
       <c r="BG3" t="n">
-        <v>26769000</v>
+        <v>25058000</v>
       </c>
       <c r="BH3" t="n">
-        <v>26769000</v>
+        <v>25058000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1206072000</v>
+        <v>1850086000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>18740000</v>
+        <v>8085000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1764513000</v>
+        <v>1560456000</v>
       </c>
       <c r="BL3" t="n">
-        <v>210405000</v>
+        <v>220233000</v>
       </c>
       <c r="BM3" t="n">
-        <v>210405000</v>
+        <v>220233000</v>
       </c>
       <c r="BN3" t="n">
-        <v>210405000</v>
+        <v>220233000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>825000000</v>
@@ -2028,43 +2028,43 @@
         <v>825000000</v>
       </c>
       <c r="D4" t="n">
-        <v>833480000</v>
+        <v>595805000</v>
       </c>
       <c r="E4" t="n">
-        <v>1057138000</v>
+        <v>809477000</v>
       </c>
       <c r="F4" t="n">
-        <v>864034000</v>
+        <v>646445000</v>
       </c>
       <c r="G4" t="n">
-        <v>1921466000</v>
+        <v>1455805000</v>
       </c>
       <c r="H4" t="n">
-        <v>516731000</v>
+        <v>377208000</v>
       </c>
       <c r="I4" t="n">
-        <v>864034000</v>
+        <v>646445000</v>
       </c>
       <c r="J4" t="n">
-        <v>3425000</v>
+        <v>3267000</v>
       </c>
       <c r="K4" t="n">
-        <v>867753000</v>
+        <v>649595000</v>
       </c>
       <c r="L4" t="n">
-        <v>946685000</v>
+        <v>729542000</v>
       </c>
       <c r="M4" t="n">
-        <v>918015000</v>
+        <v>769469000</v>
       </c>
       <c r="N4" t="n">
-        <v>50262000</v>
+        <v>119874000</v>
       </c>
       <c r="O4" t="n">
-        <v>867753000</v>
+        <v>649595000</v>
       </c>
       <c r="P4" t="n">
-        <v>79235000</v>
+        <v>183072000</v>
       </c>
       <c r="Q4" t="n">
         <v>90063000</v>
@@ -2076,146 +2076,144 @@
         <v>230000</v>
       </c>
       <c r="T4" t="n">
-        <v>3264969000</v>
+        <v>3076957000</v>
       </c>
       <c r="U4" t="n">
-        <v>92509000</v>
+        <v>91672000</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>12762000</v>
+        <v>10476000</v>
       </c>
       <c r="X4" t="n">
-        <v>79747000</v>
+        <v>81196000</v>
       </c>
       <c r="Y4" t="n">
-        <v>815000</v>
+        <v>1249000</v>
       </c>
       <c r="Z4" t="n">
-        <v>78932000</v>
+        <v>79947000</v>
       </c>
       <c r="AA4" t="n">
-        <v>3172460000</v>
+        <v>2985285000</v>
       </c>
       <c r="AB4" t="n">
-        <v>977391000</v>
+        <v>728281000</v>
       </c>
       <c r="AC4" t="n">
-        <v>2610000</v>
+        <v>2018000</v>
       </c>
       <c r="AD4" t="n">
-        <v>974781000</v>
+        <v>726263000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1612033000</v>
+        <v>1654933000</v>
       </c>
       <c r="AF4" t="n">
-        <v>261156000</v>
+        <v>159896000</v>
       </c>
       <c r="AG4" t="n">
         <v>307000</v>
       </c>
       <c r="AH4" t="n">
-        <v>113092000</v>
+        <v>105549000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1237478000</v>
+        <v>1389181000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4182984000</v>
+        <v>3846426000</v>
       </c>
       <c r="AK4" t="n">
-        <v>493793000</v>
+        <v>483933000</v>
       </c>
       <c r="AL4" t="n">
-        <v>77422000</v>
+        <v>93921000</v>
       </c>
       <c r="AM4" t="n">
-        <v>75622000</v>
+        <v>70141000</v>
       </c>
       <c r="AN4" t="n">
-        <v>75622000</v>
+        <v>70141000</v>
       </c>
       <c r="AO4" t="n">
-        <v>273172000</v>
+        <v>270151000</v>
       </c>
       <c r="AP4" t="n">
-        <v>195660000</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>75622000</v>
-      </c>
+        <v>191273000</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>77512000</v>
+        <v>78878000</v>
       </c>
       <c r="AS4" t="n">
-        <v>3719000</v>
+        <v>3150000</v>
       </c>
       <c r="AT4" t="n">
-        <v>3719000</v>
+        <v>3150000</v>
       </c>
       <c r="AU4" t="n">
-        <v>44870000</v>
+        <v>45968000</v>
       </c>
       <c r="AV4" t="n">
-        <v>-44221000</v>
+        <v>-50680000</v>
       </c>
       <c r="AW4" t="n">
-        <v>89091000</v>
+        <v>96648000</v>
       </c>
       <c r="AX4" t="n">
-        <v>46239000</v>
+        <v>49101000</v>
       </c>
       <c r="AY4" t="n">
-        <v>29243000</v>
+        <v>32904000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13609000</v>
+        <v>14643000</v>
       </c>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
         <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>3689191000</v>
+        <v>3362493000</v>
       </c>
       <c r="BD4" t="n">
-        <v>11135000</v>
+        <v>27155000</v>
       </c>
       <c r="BE4" t="n">
-        <v>22223000</v>
+        <v>20346000</v>
       </c>
       <c r="BF4" t="n">
-        <v>22755000</v>
+        <v>88493000</v>
       </c>
       <c r="BG4" t="n">
-        <v>25058000</v>
+        <v>26769000</v>
       </c>
       <c r="BH4" t="n">
-        <v>25058000</v>
+        <v>26769000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1850086000</v>
+        <v>1206072000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>8085000</v>
+        <v>18740000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1560456000</v>
+        <v>1764513000</v>
       </c>
       <c r="BL4" t="n">
-        <v>220233000</v>
+        <v>210405000</v>
       </c>
       <c r="BM4" t="n">
-        <v>220233000</v>
+        <v>210405000</v>
       </c>
       <c r="BN4" t="n">
-        <v>220233000</v>
+        <v>210405000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>825000000</v>
@@ -2224,46 +2222,46 @@
         <v>825000000</v>
       </c>
       <c r="D5" t="n">
-        <v>453036000</v>
+        <v>761882000</v>
       </c>
       <c r="E5" t="n">
-        <v>509988000</v>
+        <v>891747000</v>
       </c>
       <c r="F5" t="n">
-        <v>591696000</v>
+        <v>650789000</v>
       </c>
       <c r="G5" t="n">
-        <v>1099192000</v>
+        <v>1553635000</v>
       </c>
       <c r="H5" t="n">
-        <v>255724000</v>
+        <v>321359000</v>
       </c>
       <c r="I5" t="n">
-        <v>591696000</v>
+        <v>650789000</v>
       </c>
       <c r="J5" t="n">
-        <v>5423000</v>
+        <v>7086000</v>
       </c>
       <c r="K5" t="n">
-        <v>594627000</v>
+        <v>668974000</v>
       </c>
       <c r="L5" t="n">
-        <v>619627000</v>
+        <v>670822000</v>
       </c>
       <c r="M5" t="n">
-        <v>604077000</v>
+        <v>795192000</v>
       </c>
       <c r="N5" t="n">
-        <v>9450000</v>
+        <v>126218000</v>
       </c>
       <c r="O5" t="n">
-        <v>594627000</v>
+        <v>668974000</v>
       </c>
       <c r="P5" t="n">
-        <v>132668000</v>
+        <v>214719000</v>
       </c>
       <c r="Q5" t="n">
-        <v>90063000</v>
+        <v>70316000</v>
       </c>
       <c r="R5" t="n">
         <v>230000</v>
@@ -2272,139 +2270,141 @@
         <v>230000</v>
       </c>
       <c r="T5" t="n">
-        <v>1775710000</v>
+        <v>3588337000</v>
       </c>
       <c r="U5" t="n">
-        <v>37512000</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
+        <v>9841000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1723000</v>
+      </c>
       <c r="W5" t="n">
-        <v>10336000</v>
+        <v>1930000</v>
       </c>
       <c r="X5" t="n">
-        <v>27176000</v>
+        <v>6188000</v>
       </c>
       <c r="Y5" t="n">
-        <v>2176000</v>
+        <v>4340000</v>
       </c>
       <c r="Z5" t="n">
-        <v>25000000</v>
+        <v>1848000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1738198000</v>
+        <v>3578496000</v>
       </c>
       <c r="AB5" t="n">
-        <v>482812000</v>
+        <v>885559000</v>
       </c>
       <c r="AC5" t="n">
-        <v>3247000</v>
+        <v>2746000</v>
       </c>
       <c r="AD5" t="n">
-        <v>479565000</v>
+        <v>882813000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1099557000</v>
+        <v>1966242000</v>
       </c>
       <c r="AF5" t="n">
-        <v>119845000</v>
+        <v>261228000</v>
       </c>
       <c r="AG5" t="n">
-        <v>307000</v>
+        <v>15978000</v>
       </c>
       <c r="AH5" t="n">
-        <v>35959000</v>
+        <v>110891000</v>
       </c>
       <c r="AI5" t="n">
-        <v>943446000</v>
+        <v>1578145000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2379787000</v>
+        <v>4383529000</v>
       </c>
       <c r="AK5" t="n">
-        <v>385865000</v>
+        <v>483674000</v>
       </c>
       <c r="AL5" t="n">
-        <v>43872000</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
+        <v>105214000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>68351000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>68351000</v>
+      </c>
       <c r="AO5" t="n">
-        <v>288464000</v>
+        <v>242520000</v>
       </c>
       <c r="AP5" t="n">
-        <v>194797000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>16949000</v>
-      </c>
+        <v>166382000</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>76718000</v>
+        <v>76138000</v>
       </c>
       <c r="AS5" t="n">
-        <v>2931000</v>
+        <v>18185000</v>
       </c>
       <c r="AT5" t="n">
-        <v>2931000</v>
+        <v>18185000</v>
       </c>
       <c r="AU5" t="n">
-        <v>15971000</v>
+        <v>48859000</v>
       </c>
       <c r="AV5" t="n">
-        <v>-18588000</v>
+        <v>-62106000</v>
       </c>
       <c r="AW5" t="n">
-        <v>34559000</v>
+        <v>110965000</v>
       </c>
       <c r="AX5" t="n">
-        <v>23474000</v>
+        <v>52806000</v>
       </c>
       <c r="AY5" t="n">
-        <v>970000</v>
+        <v>35106000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10115000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
+        <v>23053000</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
         <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>1993922000</v>
+        <v>3899855000</v>
       </c>
       <c r="BD5" t="n">
-        <v>5370000</v>
+        <v>26449000</v>
       </c>
       <c r="BE5" t="n">
-        <v>12110000</v>
+        <v>15600000</v>
       </c>
       <c r="BF5" t="n">
-        <v>30271000</v>
+        <v>142000000</v>
       </c>
       <c r="BG5" t="n">
-        <v>25585000</v>
+        <v>14809000</v>
       </c>
       <c r="BH5" t="n">
-        <v>25585000</v>
+        <v>14809000</v>
       </c>
       <c r="BI5" t="n">
-        <v>867578000</v>
+        <v>1262302000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>14417000</v>
+        <v>14783000</v>
       </c>
       <c r="BK5" t="n">
-        <v>987062000</v>
+        <v>2301133000</v>
       </c>
       <c r="BL5" t="n">
-        <v>51529000</v>
+        <v>122779000</v>
       </c>
       <c r="BM5" t="n">
-        <v>51529000</v>
+        <v>122779000</v>
       </c>
       <c r="BN5" t="n">
-        <v>46673000</v>
+        <v>122779000</v>
       </c>
     </row>
   </sheetData>
@@ -2640,71 +2640,71 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-42255000</v>
+        <v>-101718000</v>
       </c>
       <c r="C2" t="n">
-        <v>-1491661000</v>
+        <v>-415000000</v>
       </c>
       <c r="D2" t="n">
-        <v>1695475000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>440198000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>91662000</v>
+      </c>
       <c r="F2" t="n">
-        <v>122779000</v>
+        <v>47495000</v>
       </c>
       <c r="G2" t="n">
-        <v>210405000</v>
+        <v>145220000</v>
       </c>
       <c r="H2" t="n">
-        <v>14000</v>
+        <v>-2000</v>
       </c>
       <c r="I2" t="n">
-        <v>-87640000</v>
+        <v>-97723000</v>
       </c>
       <c r="J2" t="n">
-        <v>34265000</v>
+        <v>9772000</v>
       </c>
       <c r="K2" t="n">
-        <v>-102963000</v>
+        <v>-64360000</v>
       </c>
       <c r="L2" t="n">
-        <v>-57698000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-4076000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-4076000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+        <v>-36019000</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>91662000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>91662000</v>
+      </c>
       <c r="Q2" t="n">
-        <v>203814000</v>
+        <v>25198000</v>
       </c>
       <c r="R2" t="n">
-        <v>203814000</v>
+        <v>25198000</v>
       </c>
       <c r="S2" t="n">
-        <v>-1491661000</v>
+        <v>-415000000</v>
       </c>
       <c r="T2" t="n">
-        <v>1695475000</v>
+        <v>440198000</v>
       </c>
       <c r="U2" t="n">
-        <v>-79650000</v>
+        <v>-5777000</v>
       </c>
       <c r="V2" t="n">
-        <v>-6909000</v>
+        <v>-2903000</v>
       </c>
       <c r="W2" t="n">
-        <v>1047000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>450000</v>
-      </c>
+        <v>9596000</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
@@ -2712,381 +2712,381 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-84616000</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-84616000</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-42255000</v>
+        <v>-101718000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-38920000</v>
+        <v>-20703000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-221348000</v>
+        <v>-208458000</v>
       </c>
       <c r="AF2" t="n">
-        <v>123225000</v>
+        <v>-46177000</v>
       </c>
       <c r="AG2" t="n">
-        <v>46303000</v>
+        <v>21211000</v>
       </c>
       <c r="AH2" t="n">
-        <v>212577000</v>
+        <v>138349000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-14934000</v>
+        <v>-10326000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>13111000</v>
+        <v>6320000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-601630000</v>
+        <v>-317835000</v>
       </c>
       <c r="AL2" t="n">
-        <v>48708000</v>
+        <v>28300000</v>
       </c>
       <c r="AM2" t="n">
-        <v>15245000</v>
+        <v>5632000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1795000</v>
+        <v>393000</v>
       </c>
       <c r="AO2" t="n">
-        <v>13450000</v>
+        <v>5239000</v>
       </c>
       <c r="AP2" t="n">
-        <v>2520000</v>
+        <v>-108000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>912000</v>
+        <v>168000</v>
       </c>
       <c r="AR2" t="n">
-        <v>45374000</v>
+        <v>37006000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>221526000</v>
+        <v>99346000</v>
       </c>
       <c r="C3" t="n">
-        <v>-1584204000</v>
+        <v>-1047181000</v>
       </c>
       <c r="D3" t="n">
-        <v>1921151000</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>1476558000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
       <c r="F3" t="n">
-        <v>210405000</v>
+        <v>220233000</v>
       </c>
       <c r="G3" t="n">
-        <v>220233000</v>
+        <v>88870000</v>
       </c>
       <c r="H3" t="n">
         <v>2000</v>
       </c>
       <c r="I3" t="n">
-        <v>-9830000</v>
+        <v>131361000</v>
       </c>
       <c r="J3" t="n">
-        <v>-396333000</v>
+        <v>116036000</v>
       </c>
       <c r="K3" t="n">
-        <v>-662053000</v>
+        <v>-246933000</v>
       </c>
       <c r="L3" t="n">
-        <v>-66171000</v>
+        <v>-63374000</v>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q3" t="n">
-        <v>336947000</v>
+        <v>429377000</v>
       </c>
       <c r="R3" t="n">
-        <v>336947000</v>
+        <v>429377000</v>
       </c>
       <c r="S3" t="n">
-        <v>-1584204000</v>
+        <v>-1047181000</v>
       </c>
       <c r="T3" t="n">
-        <v>1921151000</v>
+        <v>1476558000</v>
       </c>
       <c r="U3" t="n">
-        <v>164977000</v>
+        <v>-84021000</v>
       </c>
       <c r="V3" t="n">
-        <v>-11246000</v>
+        <v>-12366000</v>
       </c>
       <c r="W3" t="n">
-        <v>1044000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
+        <v>5625000</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>-317963000</v>
+        <v>-8161000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-317963000</v>
+        <v>-8161000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-4721000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-4721000</v>
       </c>
       <c r="AC3" t="n">
-        <v>221526000</v>
+        <v>99346000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-9889000</v>
+        <v>-18138000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-122866000</v>
+        <v>13341000</v>
       </c>
       <c r="AF3" t="n">
-        <v>30992000</v>
+        <v>356044000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-44808000</v>
+        <v>57854000</v>
       </c>
       <c r="AH3" t="n">
-        <v>151703000</v>
+        <v>-99066000</v>
       </c>
       <c r="AI3" t="n">
-        <v>93351000</v>
+        <v>-81963000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-17731000</v>
+        <v>-227000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-336373000</v>
+        <v>-219301000</v>
       </c>
       <c r="AL3" t="n">
-        <v>55184000</v>
+        <v>56784000</v>
       </c>
       <c r="AM3" t="n">
-        <v>13107000</v>
+        <v>12957000</v>
       </c>
       <c r="AN3" t="n">
-        <v>502000</v>
+        <v>491000</v>
       </c>
       <c r="AO3" t="n">
-        <v>12605000</v>
+        <v>12466000</v>
       </c>
       <c r="AP3" t="n">
-        <v>8615000</v>
+        <v>231000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>277000</v>
+        <v>7377000</v>
       </c>
       <c r="AR3" t="n">
-        <v>172652000</v>
+        <v>-114749000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>99346000</v>
+        <v>221526000</v>
       </c>
       <c r="C4" t="n">
-        <v>-1047181000</v>
+        <v>-1584204000</v>
       </c>
       <c r="D4" t="n">
-        <v>1476558000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
+        <v>1921151000</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
+        <v>210405000</v>
+      </c>
+      <c r="G4" t="n">
         <v>220233000</v>
-      </c>
-      <c r="G4" t="n">
-        <v>88870000</v>
       </c>
       <c r="H4" t="n">
         <v>2000</v>
       </c>
       <c r="I4" t="n">
-        <v>131361000</v>
+        <v>-9830000</v>
       </c>
       <c r="J4" t="n">
-        <v>116036000</v>
+        <v>-396333000</v>
       </c>
       <c r="K4" t="n">
-        <v>-246933000</v>
+        <v>-662053000</v>
       </c>
       <c r="L4" t="n">
-        <v>-63374000</v>
+        <v>-66171000</v>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
+      <c r="N4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="n">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>336947000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>336947000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-1584204000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1921151000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>164977000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-11246000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1044000</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>429377000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>429377000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-1047181000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1476558000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-84021000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-12366000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>5625000</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>-8161000</v>
+        <v>-317963000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-8161000</v>
+        <v>-317963000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-4721000</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-4721000</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>99346000</v>
+        <v>221526000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-18138000</v>
+        <v>-9889000</v>
       </c>
       <c r="AE4" t="n">
-        <v>13341000</v>
+        <v>-122866000</v>
       </c>
       <c r="AF4" t="n">
-        <v>356044000</v>
+        <v>30992000</v>
       </c>
       <c r="AG4" t="n">
-        <v>57854000</v>
+        <v>-44808000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-99066000</v>
+        <v>151703000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-81963000</v>
+        <v>93351000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-227000</v>
+        <v>-17731000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-219301000</v>
+        <v>-336373000</v>
       </c>
       <c r="AL4" t="n">
-        <v>56784000</v>
+        <v>55184000</v>
       </c>
       <c r="AM4" t="n">
-        <v>12957000</v>
+        <v>13107000</v>
       </c>
       <c r="AN4" t="n">
-        <v>491000</v>
+        <v>502000</v>
       </c>
       <c r="AO4" t="n">
-        <v>12466000</v>
+        <v>12605000</v>
       </c>
       <c r="AP4" t="n">
-        <v>231000</v>
+        <v>8615000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7377000</v>
+        <v>277000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-114749000</v>
+        <v>172652000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-101718000</v>
+        <v>-42255000</v>
       </c>
       <c r="C5" t="n">
-        <v>-415000000</v>
+        <v>-1491661000</v>
       </c>
       <c r="D5" t="n">
-        <v>440198000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>91662000</v>
-      </c>
+        <v>1695475000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>47495000</v>
+        <v>122779000</v>
       </c>
       <c r="G5" t="n">
-        <v>145220000</v>
+        <v>210405000</v>
       </c>
       <c r="H5" t="n">
-        <v>-2000</v>
+        <v>14000</v>
       </c>
       <c r="I5" t="n">
-        <v>-97723000</v>
+        <v>-87640000</v>
       </c>
       <c r="J5" t="n">
-        <v>9772000</v>
+        <v>34265000</v>
       </c>
       <c r="K5" t="n">
-        <v>-64360000</v>
+        <v>-102963000</v>
       </c>
       <c r="L5" t="n">
-        <v>-36019000</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
-        <v>91662000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>91662000</v>
-      </c>
+        <v>-57698000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-4076000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-4076000</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>25198000</v>
+        <v>203814000</v>
       </c>
       <c r="R5" t="n">
-        <v>25198000</v>
+        <v>203814000</v>
       </c>
       <c r="S5" t="n">
-        <v>-415000000</v>
+        <v>-1491661000</v>
       </c>
       <c r="T5" t="n">
-        <v>440198000</v>
+        <v>1695475000</v>
       </c>
       <c r="U5" t="n">
-        <v>-5777000</v>
+        <v>-79650000</v>
       </c>
       <c r="V5" t="n">
-        <v>-2903000</v>
+        <v>-6909000</v>
       </c>
       <c r="W5" t="n">
-        <v>9596000</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
+        <v>1047000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>450000</v>
+      </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
@@ -3094,58 +3094,58 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>-84616000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-84616000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-101718000</v>
+        <v>-42255000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-20703000</v>
+        <v>-38920000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-208458000</v>
+        <v>-221348000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-46177000</v>
+        <v>123225000</v>
       </c>
       <c r="AG5" t="n">
-        <v>21211000</v>
+        <v>46303000</v>
       </c>
       <c r="AH5" t="n">
-        <v>138349000</v>
+        <v>212577000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-10326000</v>
+        <v>-14934000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6320000</v>
+        <v>13111000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-317835000</v>
+        <v>-601630000</v>
       </c>
       <c r="AL5" t="n">
-        <v>28300000</v>
+        <v>48708000</v>
       </c>
       <c r="AM5" t="n">
-        <v>5632000</v>
+        <v>15245000</v>
       </c>
       <c r="AN5" t="n">
-        <v>393000</v>
+        <v>1795000</v>
       </c>
       <c r="AO5" t="n">
-        <v>5239000</v>
+        <v>13450000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-108000</v>
+        <v>2520000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>168000</v>
+        <v>912000</v>
       </c>
       <c r="AR5" t="n">
-        <v>37006000</v>
+        <v>45374000</v>
       </c>
     </row>
   </sheetData>
@@ -3680,177 +3680,177 @@
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>prevName</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>nameChangeDate</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
         </is>
       </c>
       <c r="EI1" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Haitao  Liu', 'age': 49, 'title': 'CEO &amp; Vice-Chairman of the Board', 'yearBorn': 1976, 'fiscalYear': 2025, 'totalPay': 749512, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yan  Wang', 'age': 44, 'title': 'CFO &amp; Executive Director', 'yearBorn': 1981, 'fiscalYear': 2025, 'totalPay': 632509, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xuesong  Wang', 'age': 50, 'title': 'Chief Engineer', 'yearBorn': 1975, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Hin Chi  Tsui', 'age': 38, 'title': 'Company Secretary', 'yearBorn': 1987, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Haitao  Liu', 'age': 49, 'title': 'CEO &amp; Vice-Chairman of the Board', 'yearBorn': 1976, 'fiscalYear': 2025, 'totalPay': 748914, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yan  Wang', 'age': 44, 'title': 'CFO &amp; Executive Director', 'yearBorn': 1981, 'fiscalYear': 2025, 'totalPay': 632005, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xuesong  Wang', 'age': 50, 'title': 'Chief Engineer', 'yearBorn': 1975, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Hin Chi  Tsui', 'age': 38, 'title': 'Company Secretary', 'yearBorn': 1987, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -3948,28 +3948,28 @@
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>0.212</v>
+        <v>0.195</v>
       </c>
       <c r="U2" t="n">
-        <v>0.212</v>
+        <v>0.187</v>
       </c>
       <c r="V2" t="n">
-        <v>0.212</v>
+        <v>0.185</v>
       </c>
       <c r="W2" t="n">
-        <v>0.212</v>
+        <v>0.222</v>
       </c>
       <c r="X2" t="n">
-        <v>0.212</v>
+        <v>0.195</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.212</v>
+        <v>0.187</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.212</v>
+        <v>0.185</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.212</v>
+        <v>0.222</v>
       </c>
       <c r="AB2" t="n">
         <v>1719878400</v>
@@ -3978,58 +3978,58 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.787</v>
+        <v>0.726</v>
       </c>
       <c r="AE2" t="n">
-        <v>7.0666666</v>
+        <v>7.3</v>
       </c>
       <c r="AF2" t="n">
-        <v>90000</v>
+        <v>842000</v>
       </c>
       <c r="AG2" t="n">
-        <v>90000</v>
+        <v>842000</v>
       </c>
       <c r="AH2" t="n">
-        <v>4605546</v>
+        <v>843844</v>
       </c>
       <c r="AI2" t="n">
-        <v>616400</v>
+        <v>385800</v>
       </c>
       <c r="AJ2" t="n">
-        <v>616400</v>
+        <v>385800</v>
       </c>
       <c r="AK2" t="n">
         <v>0.19</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.212</v>
+        <v>0.191</v>
       </c>
       <c r="AM2" t="n">
-        <v>174900000</v>
+        <v>180674992</v>
       </c>
       <c r="AN2" t="n">
-        <v>168300000</v>
+        <v>160875000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.187</v>
+        <v>0.185</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.890000000000001</v>
+        <v>7.33</v>
       </c>
       <c r="AQ2" t="n">
         <v>10.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.187</v>
+        <v>0.185</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.10673224</v>
+        <v>0.11025642</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.29726</v>
+        <v>0.25926</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.72279</v>
+        <v>1.44269</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>778872000</v>
+        <v>784646976</v>
       </c>
       <c r="BA2" t="n">
         <v>0.0134000005</v>
@@ -4061,16 +4061,16 @@
         <v>0.71002</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.00219</v>
+        <v>0.00229</v>
       </c>
       <c r="BF2" t="n">
         <v>825000000</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.976566</v>
+        <v>0.97579545</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.21708721</v>
+        <v>0.22443227</v>
       </c>
       <c r="BI2" t="n">
         <v>1767139200</v>
@@ -4096,16 +4096,16 @@
         <v>1722470400</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.475</v>
+        <v>0.479</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.228</v>
+        <v>4.259</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0.9758267</v>
+        <v>-0.97076464</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BT2" t="n">
         <v>0.026</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="BW2" t="n">
-        <v>0.212</v>
+        <v>0.219</v>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
@@ -4220,139 +4220,139 @@
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>PRE</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DA2" t="n">
+        <v>1782115039</v>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>finmb_699219046</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DF2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>12.307694</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="DK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>1609896600000</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>0.024000004</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>0.185 - 0.222</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DP2" t="n">
+        <v>843844</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0.033999994</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0.18378375</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>0.185 - 7.33</t>
+        </is>
+      </c>
+      <c r="DT2" t="n">
+        <v>-7.111</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>-0.9701228</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-97.07646</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>ZONQING LTD</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
           <t>ZONQING Environmental Limited</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DB2" t="n">
-        <v>4605546</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>0.024999991</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>0.13368979</v>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>0.187 - 8.89</t>
-        </is>
-      </c>
-      <c r="DF2" t="n">
-        <v>-8.678000000000001</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>-0.976153</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>-97.58266399999999</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="DJ2" t="n">
+      <c r="DZ2" t="n">
+        <v>-0.040260002</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>-0.15528813</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-1.22369</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>-0.84820026</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>Zonbong Landscape Environmental Limited</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="EH2" t="b">
         <v>0</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>0.212</v>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>ZONQING LTD</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DN2" t="n">
-        <v>1780450634</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>finmb_699219046</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DS2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.08525998999999999</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.2868196</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-1.51079</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.87694377</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>Zonbong Landscape Environmental Limited</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="ED2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>1609896600000</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>0.212 - 0.212</t>
-        </is>
       </c>
       <c r="EI2" t="inlineStr"/>
     </row>
